--- a/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\banhao-xiugai\BanHao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\StartConfig\BanHao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2EE126-5B59-447A-A000-748305062F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADBA92F-F037-404E-A919-8FFF37BC4A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2610" yWindow="1440" windowWidth="24990" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -639,7 +639,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>28</v>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="5">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="5">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>14</v>
@@ -708,8 +708,8 @@
       <c r="D10" s="3">
         <v>1</v>
       </c>
-      <c r="E10" s="3">
-        <v>1</v>
+      <c r="E10" s="5">
+        <v>201</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>31</v>
@@ -729,8 +729,8 @@
       <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="3">
-        <v>1</v>
+      <c r="E11" s="5">
+        <v>201</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>18</v>
@@ -748,8 +748,8 @@
       <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="3">
-        <v>1</v>
+      <c r="E12" s="5">
+        <v>201</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>19</v>
@@ -766,8 +766,8 @@
       <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E13" s="3">
-        <v>1</v>
+      <c r="E13" s="5">
+        <v>201</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>20</v>
@@ -784,8 +784,8 @@
       <c r="D14" s="5">
         <v>1</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
+      <c r="E14" s="5">
+        <v>201</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>21</v>
@@ -802,8 +802,8 @@
       <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="3">
-        <v>1</v>
+      <c r="E15" s="5">
+        <v>201</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>22</v>
@@ -820,8 +820,8 @@
       <c r="D16" s="5">
         <v>1</v>
       </c>
-      <c r="E16" s="3">
-        <v>1</v>
+      <c r="E16" s="5">
+        <v>201</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>23</v>
@@ -838,8 +838,8 @@
       <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="3">
-        <v>1</v>
+      <c r="E17" s="5">
+        <v>201</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>24</v>
@@ -856,8 +856,8 @@
       <c r="D18" s="5">
         <v>1</v>
       </c>
-      <c r="E18" s="3">
-        <v>1</v>
+      <c r="E18" s="5">
+        <v>201</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>25</v>
@@ -874,8 +874,8 @@
       <c r="D19" s="5">
         <v>1</v>
       </c>
-      <c r="E19" s="3">
-        <v>1</v>
+      <c r="E19" s="5">
+        <v>201</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>27</v>
@@ -892,8 +892,8 @@
       <c r="D20" s="5">
         <v>1</v>
       </c>
-      <c r="E20" s="3">
-        <v>1</v>
+      <c r="E20" s="5">
+        <v>201</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>35</v>
@@ -910,8 +910,8 @@
       <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="3">
-        <v>1</v>
+      <c r="E21" s="5">
+        <v>201</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>37</v>
@@ -929,8 +929,8 @@
       <c r="D22" s="5">
         <v>1</v>
       </c>
-      <c r="E22" s="3">
-        <v>1</v>
+      <c r="E22" s="5">
+        <v>201</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>38</v>
@@ -948,8 +948,8 @@
       <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" s="3">
-        <v>1</v>
+      <c r="E23" s="5">
+        <v>201</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>38</v>

--- a/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\StartConfig\BanHao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADBA92F-F037-404E-A919-8FFF37BC4A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D349E5-127E-4DAE-8980-D7304EDF0389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1440" windowWidth="24990" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="1200" windowWidth="24990" windowHeight="13410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
     <sheet name="中心区" sheetId="3" r:id="rId2"/>
+    <sheet name="Robot区" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -165,13 +166,19 @@
   <si>
     <t>Map102</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>Robot01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +204,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1309,4 +1321,182 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2515949-202F-4D8F-8697-4C539F7E6A32}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="5">
+        <v>20302</v>
+      </c>
+      <c r="D6" s="5">
+        <v>203</v>
+      </c>
+      <c r="E6" s="5">
+        <v>203</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="50">
   <si>
     <t>Id</t>
   </si>
@@ -73,7 +73,7 @@
     <t>#20004-20100</t>
   </si>
   <si>
-    <t>#3区封测区</t>
+    <t>#201版号区</t>
   </si>
   <si>
     <t>Account</t>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Happy</t>
-  </si>
-  <si>
-    <t>#5区</t>
   </si>
   <si>
     <t>Center</t>
@@ -1187,7 +1184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O58"/>
+  <dimension ref="A3:O57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1199,7 +1196,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" spans="1:15">
       <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" spans="1:15">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" spans="1:15">
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1276,10 +1273,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8">
-        <v>301</v>
+        <v>20101</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -1301,12 +1298,14 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:15">
+    <row r="8" spans="1:15">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="8">
-        <v>302</v>
+        <v>20102</v>
       </c>
       <c r="D8" s="5">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -1317,23 +1316,16 @@
       <c r="G8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="3">
         <v>20326</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="3:8">
+    </row>
+    <row r="9" spans="1:15">
       <c r="C9" s="8">
-        <v>303</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3</v>
+        <v>20103</v>
+      </c>
+      <c r="D9" s="3">
+        <v>201</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -1348,12 +1340,12 @@
         <v>20327</v>
       </c>
     </row>
-    <row r="10" spans="3:8">
+    <row r="10" spans="1:15">
       <c r="C10" s="8">
-        <v>304</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
+        <v>20104</v>
+      </c>
+      <c r="D10" s="5">
+        <v>201</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -1364,16 +1356,16 @@
       <c r="G10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="3">
         <v>20328</v>
       </c>
     </row>
-    <row r="11" spans="3:7">
+    <row r="11" spans="1:15">
       <c r="C11" s="8">
-        <v>305</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3</v>
+        <v>20105</v>
+      </c>
+      <c r="D11" s="3">
+        <v>201</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -1385,12 +1377,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:7">
+    <row r="12" spans="1:15">
       <c r="C12" s="8">
-        <v>306</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
+        <v>20106</v>
+      </c>
+      <c r="D12" s="5">
+        <v>201</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -1402,12 +1394,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:7">
+    <row r="13" spans="1:15">
       <c r="C13" s="8">
-        <v>307</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3</v>
+        <v>20107</v>
+      </c>
+      <c r="D13" s="3">
+        <v>201</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -1419,12 +1411,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="3:7">
+    <row r="14" spans="1:15">
       <c r="C14" s="8">
-        <v>308</v>
+        <v>20108</v>
       </c>
       <c r="D14" s="5">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -1436,12 +1428,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
+    <row r="15" spans="1:15">
       <c r="C15" s="8">
-        <v>309</v>
+        <v>20109</v>
       </c>
       <c r="D15" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -1453,12 +1445,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
+    <row r="16" spans="1:15">
       <c r="C16" s="8">
-        <v>310</v>
+        <v>20110</v>
       </c>
       <c r="D16" s="5">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
@@ -1472,10 +1464,10 @@
     </row>
     <row r="17" spans="3:7">
       <c r="C17" s="8">
-        <v>311</v>
-      </c>
-      <c r="D17" s="5">
-        <v>3</v>
+        <v>20111</v>
+      </c>
+      <c r="D17" s="3">
+        <v>201</v>
       </c>
       <c r="E17" s="5">
         <v>1</v>
@@ -1489,10 +1481,10 @@
     </row>
     <row r="18" spans="3:7">
       <c r="C18" s="8">
-        <v>312</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
+        <v>20112</v>
+      </c>
+      <c r="D18" s="5">
+        <v>201</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
@@ -1506,10 +1498,10 @@
     </row>
     <row r="19" spans="3:7">
       <c r="C19" s="8">
-        <v>313</v>
-      </c>
-      <c r="D19" s="5">
-        <v>3</v>
+        <v>20113</v>
+      </c>
+      <c r="D19" s="3">
+        <v>201</v>
       </c>
       <c r="E19" s="5">
         <v>1</v>
@@ -1523,10 +1515,10 @@
     </row>
     <row r="20" spans="3:7">
       <c r="C20" s="8">
-        <v>314</v>
+        <v>20114</v>
       </c>
       <c r="D20" s="5">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E20" s="5">
         <v>1</v>
@@ -1540,10 +1532,10 @@
     </row>
     <row r="21" spans="3:7">
       <c r="C21" s="8">
-        <v>315</v>
+        <v>20115</v>
       </c>
       <c r="D21" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E21" s="5">
         <v>1</v>
@@ -1557,10 +1549,10 @@
     </row>
     <row r="22" spans="3:7">
       <c r="C22" s="8">
-        <v>316</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3</v>
+        <v>20116</v>
+      </c>
+      <c r="D22" s="5">
+        <v>201</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
@@ -1574,10 +1566,10 @@
     </row>
     <row r="23" spans="3:7">
       <c r="C23" s="8">
-        <v>317</v>
-      </c>
-      <c r="D23" s="5">
-        <v>3</v>
+        <v>20117</v>
+      </c>
+      <c r="D23" s="3">
+        <v>201</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
@@ -1591,10 +1583,10 @@
     </row>
     <row r="24" spans="3:7">
       <c r="C24" s="8">
-        <v>318</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3</v>
+        <v>20118</v>
+      </c>
+      <c r="D24" s="5">
+        <v>201</v>
       </c>
       <c r="E24" s="5">
         <v>1</v>
@@ -1608,10 +1600,10 @@
     </row>
     <row r="25" spans="3:7">
       <c r="C25" s="8">
-        <v>319</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3</v>
+        <v>20119</v>
+      </c>
+      <c r="D25" s="3">
+        <v>201</v>
       </c>
       <c r="E25" s="5">
         <v>1</v>
@@ -1625,10 +1617,10 @@
     </row>
     <row r="26" spans="3:7">
       <c r="C26" s="8">
-        <v>320</v>
-      </c>
-      <c r="D26" s="3">
-        <v>3</v>
+        <v>20120</v>
+      </c>
+      <c r="D26" s="5">
+        <v>201</v>
       </c>
       <c r="E26" s="3">
         <v>1</v>
@@ -1642,10 +1634,10 @@
     </row>
     <row r="27" spans="3:7">
       <c r="C27" s="8">
-        <v>321</v>
+        <v>20121</v>
       </c>
       <c r="D27" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E27" s="5">
         <v>1</v>
@@ -1659,10 +1651,10 @@
     </row>
     <row r="28" spans="3:7">
       <c r="C28" s="8">
-        <v>322</v>
-      </c>
-      <c r="D28" s="3">
-        <v>3</v>
+        <v>20122</v>
+      </c>
+      <c r="D28" s="5">
+        <v>201</v>
       </c>
       <c r="E28" s="5">
         <v>1</v>
@@ -1676,10 +1668,10 @@
     </row>
     <row r="29" spans="3:7">
       <c r="C29" s="8">
-        <v>323</v>
+        <v>20123</v>
       </c>
       <c r="D29" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E29" s="5">
         <v>1</v>
@@ -1693,10 +1685,10 @@
     </row>
     <row r="30" spans="3:7">
       <c r="C30" s="8">
-        <v>324</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3</v>
+        <v>20124</v>
+      </c>
+      <c r="D30" s="5">
+        <v>201</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -1710,10 +1702,10 @@
     </row>
     <row r="31" spans="3:7">
       <c r="C31" s="8">
-        <v>325</v>
+        <v>20125</v>
       </c>
       <c r="D31" s="3">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="E31" s="5">
         <v>1</v>
@@ -1725,450 +1717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="8">
-        <v>501</v>
-      </c>
-      <c r="D33" s="3">
-        <v>5</v>
-      </c>
-      <c r="E33" s="5">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" s="3">
-        <v>20335</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="8">
-        <v>502</v>
-      </c>
-      <c r="D34" s="5">
-        <v>5</v>
-      </c>
-      <c r="E34" s="5">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="3">
-        <v>20336</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8">
-      <c r="C35" s="8">
-        <v>503</v>
-      </c>
-      <c r="D35" s="3">
-        <v>5</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="3">
-        <v>20337</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8">
-      <c r="C36" s="8">
-        <v>504</v>
-      </c>
-      <c r="D36" s="5">
-        <v>5</v>
-      </c>
-      <c r="E36" s="3">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="3">
-        <v>20338</v>
-      </c>
-    </row>
-    <row r="37" spans="3:7">
-      <c r="C37" s="8">
-        <v>505</v>
-      </c>
-      <c r="D37" s="3">
-        <v>5</v>
-      </c>
-      <c r="E37" s="5">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="3:7">
-      <c r="C38" s="8">
-        <v>506</v>
-      </c>
-      <c r="D38" s="5">
-        <v>5</v>
-      </c>
-      <c r="E38" s="5">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7">
-      <c r="C39" s="8">
-        <v>507</v>
-      </c>
-      <c r="D39" s="3">
-        <v>5</v>
-      </c>
-      <c r="E39" s="5">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7">
-      <c r="C40" s="8">
-        <v>508</v>
-      </c>
-      <c r="D40" s="5">
-        <v>5</v>
-      </c>
-      <c r="E40" s="3">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="3:7">
-      <c r="C41" s="8">
-        <v>509</v>
-      </c>
-      <c r="D41" s="3">
-        <v>5</v>
-      </c>
-      <c r="E41" s="5">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="3:7">
-      <c r="C42" s="8">
-        <v>510</v>
-      </c>
-      <c r="D42" s="5">
-        <v>5</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="3:7">
-      <c r="C43" s="8">
-        <v>511</v>
-      </c>
-      <c r="D43" s="3">
-        <v>5</v>
-      </c>
-      <c r="E43" s="5">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="3:7">
-      <c r="C44" s="8">
-        <v>512</v>
-      </c>
-      <c r="D44" s="5">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="3:7">
-      <c r="C45" s="8">
-        <v>513</v>
-      </c>
-      <c r="D45" s="3">
-        <v>5</v>
-      </c>
-      <c r="E45" s="5">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="3:7">
-      <c r="C46" s="8">
-        <v>514</v>
-      </c>
-      <c r="D46" s="5">
-        <v>5</v>
-      </c>
-      <c r="E46" s="5">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="3:7">
-      <c r="C47" s="8">
-        <v>515</v>
-      </c>
-      <c r="D47" s="3">
-        <v>5</v>
-      </c>
-      <c r="E47" s="5">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="3:7">
-      <c r="C48" s="8">
-        <v>516</v>
-      </c>
-      <c r="D48" s="5">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7">
-      <c r="C49" s="8">
-        <v>517</v>
-      </c>
-      <c r="D49" s="3">
-        <v>5</v>
-      </c>
-      <c r="E49" s="5">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="3:7">
-      <c r="C50" s="8">
-        <v>518</v>
-      </c>
-      <c r="D50" s="5">
-        <v>5</v>
-      </c>
-      <c r="E50" s="5">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="3:7">
-      <c r="C51" s="8">
-        <v>519</v>
-      </c>
-      <c r="D51" s="3">
-        <v>5</v>
-      </c>
-      <c r="E51" s="5">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7">
-      <c r="C52" s="8">
-        <v>520</v>
-      </c>
-      <c r="D52" s="5">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="3:7">
-      <c r="C53" s="8">
-        <v>521</v>
-      </c>
-      <c r="D53" s="3">
-        <v>5</v>
-      </c>
-      <c r="E53" s="5">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="3:7">
-      <c r="C54" s="8">
-        <v>522</v>
-      </c>
-      <c r="D54" s="5">
-        <v>5</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="3:7">
-      <c r="C55" s="8">
-        <v>523</v>
-      </c>
-      <c r="D55" s="3">
-        <v>5</v>
-      </c>
-      <c r="E55" s="5">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="3:7">
-      <c r="C56" s="8">
-        <v>524</v>
-      </c>
-      <c r="D56" s="5">
-        <v>5</v>
-      </c>
-      <c r="E56" s="3">
-        <v>1</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="3:7">
-      <c r="C57" s="8">
-        <v>525</v>
-      </c>
-      <c r="D57" s="3">
-        <v>5</v>
-      </c>
-      <c r="E57" s="5">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" ht="13.5" customHeight="1"/>
+    <row r="57" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2286,14 +1835,14 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="14.25" spans="3:8">
+    <row r="7" s="1" customFormat="1" ht="14.25" spans="1:8">
       <c r="C7" s="5">
         <v>20202</v>
       </c>
@@ -2304,14 +1853,14 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="14.25" spans="3:8">
+    <row r="8" s="2" customFormat="1" ht="14.25" spans="1:8">
       <c r="C8" s="5">
         <v>20203</v>
       </c>
@@ -2322,14 +1871,14 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" ht="14.25" spans="3:8">
+    <row r="9" ht="14.25" spans="1:8">
       <c r="C9" s="5">
         <v>20204</v>
       </c>
@@ -2340,16 +1889,16 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="3:7">
+    <row r="10" ht="14.25" spans="1:8">
       <c r="C10" s="5">
         <v>20205</v>
       </c>
@@ -2360,10 +1909,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2458,14 +2007,14 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="8" spans="7:7">
+    <row r="8" spans="3:8">
       <c r="G8" s="1"/>
     </row>
   </sheetData>

--- a/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/BanHao/StartSceneConfig@s.xlsx
@@ -73,7 +73,7 @@
     <t>#20004-20100</t>
   </si>
   <si>
-    <t>#201版号区</t>
+    <t>#版号区</t>
   </si>
   <si>
     <t>Account</t>
@@ -1273,10 +1273,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8">
-        <v>20101</v>
+        <v>301</v>
       </c>
       <c r="D7" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -1302,10 +1302,10 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="8">
-        <v>20102</v>
+        <v>302</v>
       </c>
       <c r="D8" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="9" spans="1:15">
       <c r="C9" s="8">
-        <v>20103</v>
+        <v>303</v>
       </c>
       <c r="D9" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="10" spans="1:15">
       <c r="C10" s="8">
-        <v>20104</v>
+        <v>304</v>
       </c>
       <c r="D10" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="11" spans="1:15">
       <c r="C11" s="8">
-        <v>20105</v>
+        <v>305</v>
       </c>
       <c r="D11" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:15">
       <c r="C12" s="8">
-        <v>20106</v>
+        <v>306</v>
       </c>
       <c r="D12" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="13" spans="1:15">
       <c r="C13" s="8">
-        <v>20107</v>
+        <v>307</v>
       </c>
       <c r="D13" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="14" spans="1:15">
       <c r="C14" s="8">
-        <v>20108</v>
+        <v>308</v>
       </c>
       <c r="D14" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="15" spans="1:15">
       <c r="C15" s="8">
-        <v>20109</v>
+        <v>309</v>
       </c>
       <c r="D15" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="16" spans="1:15">
       <c r="C16" s="8">
-        <v>20110</v>
+        <v>310</v>
       </c>
       <c r="D16" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="17" spans="3:7">
       <c r="C17" s="8">
-        <v>20111</v>
+        <v>311</v>
       </c>
       <c r="D17" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5">
         <v>1</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="18" spans="3:7">
       <c r="C18" s="8">
-        <v>20112</v>
+        <v>312</v>
       </c>
       <c r="D18" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="19" spans="3:7">
       <c r="C19" s="8">
-        <v>20113</v>
+        <v>313</v>
       </c>
       <c r="D19" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5">
         <v>1</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="20" spans="3:7">
       <c r="C20" s="8">
-        <v>20114</v>
+        <v>314</v>
       </c>
       <c r="D20" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E20" s="5">
         <v>1</v>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="21" spans="3:7">
       <c r="C21" s="8">
-        <v>20115</v>
+        <v>315</v>
       </c>
       <c r="D21" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5">
         <v>1</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="22" spans="3:7">
       <c r="C22" s="8">
-        <v>20116</v>
+        <v>316</v>
       </c>
       <c r="D22" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="23" spans="3:7">
       <c r="C23" s="8">
-        <v>20117</v>
+        <v>317</v>
       </c>
       <c r="D23" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="24" spans="3:7">
       <c r="C24" s="8">
-        <v>20118</v>
+        <v>318</v>
       </c>
       <c r="D24" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5">
         <v>1</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="25" spans="3:7">
       <c r="C25" s="8">
-        <v>20119</v>
+        <v>319</v>
       </c>
       <c r="D25" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5">
         <v>1</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="26" spans="3:7">
       <c r="C26" s="8">
-        <v>20120</v>
+        <v>320</v>
       </c>
       <c r="D26" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3">
         <v>1</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="27" spans="3:7">
       <c r="C27" s="8">
-        <v>20121</v>
+        <v>321</v>
       </c>
       <c r="D27" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5">
         <v>1</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="28" spans="3:7">
       <c r="C28" s="8">
-        <v>20122</v>
+        <v>322</v>
       </c>
       <c r="D28" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E28" s="5">
         <v>1</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="29" spans="3:7">
       <c r="C29" s="8">
-        <v>20123</v>
+        <v>323</v>
       </c>
       <c r="D29" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5">
         <v>1</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="30" spans="3:7">
       <c r="C30" s="8">
-        <v>20124</v>
+        <v>324</v>
       </c>
       <c r="D30" s="5">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="31" spans="3:7">
       <c r="C31" s="8">
-        <v>20125</v>
+        <v>325</v>
       </c>
       <c r="D31" s="3">
-        <v>201</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5">
         <v>1</v>
